--- a/survey_templates/050_ethical_consumerism_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/050_ethical_consumerism_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>animal_welfare</t>
+          <t>animal welfare</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fair_trade</t>
+          <t>fair trade</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gender_equality</t>
+          <t>gender equality</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>human_rights</t>
+          <t>human rights</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>labor_practice</t>
+          <t>labor practice</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>worker_rights</t>
+          <t>worker rights</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>often_choose</t>
+          <t>often choose</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sometimes_choose</t>
+          <t>sometimes choose</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rarely_choose</t>
+          <t>rarely choose</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>never_choose</t>
+          <t>never choose</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not_very_aware</t>
+          <t>not very aware</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>not_at_all_aware</t>
+          <t>not at all aware</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>not_at_all_likely</t>
+          <t>not at all likely</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>often_choose</t>
+          <t>often choose</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sometimes_choose</t>
+          <t>sometimes choose</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rarely_choose</t>
+          <t>rarely choose</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>never_choose</t>
+          <t>never choose</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>very_frequent</t>
+          <t>very frequent</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fairly_frequent</t>
+          <t>fairly frequent</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>not_frequent</t>
+          <t>not frequent</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>very_infrequent</t>
+          <t>very infrequent</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>not_at_all_likely</t>
+          <t>not at all likely</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>not_at_all_aware</t>
+          <t>not at all aware</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>often_have</t>
+          <t>often have</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sometimes_have</t>
+          <t>sometimes have</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>rarely_have</t>
+          <t>rarely have</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>never_have</t>
+          <t>never have</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>not_at_all_aware</t>
+          <t>not at all aware</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>not_at_all_aware</t>
+          <t>not at all aware</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>very_aware</t>
+          <t>very aware</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>somewhat_aware</t>
+          <t>somewhat aware</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>not_aware</t>
+          <t>not aware</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>not_at_all_aware</t>
+          <t>not at all aware</t>
         </is>
       </c>
     </row>
